--- a/data/hex_xlsx/METSB.HE.xlsx
+++ b/data/hex_xlsx/METSB.HE.xlsx
@@ -12722,7 +12722,10 @@
       <c r="P40" s="18">
         <v>2359.69</v>
       </c>
-      <c r="Q40" s="15"/>
+      <c r="Q40" s="15">
+        <f>Q41+Q42</f>
+        <v>3177.44</v>
+      </c>
       <c r="R40" s="18">
         <v>4122.03</v>
       </c>
@@ -14213,13 +14216,34 @@
       <c r="P71" s="18">
         <v>7281.01</v>
       </c>
-      <c r="Q71" s="15"/>
-      <c r="R71" s="15"/>
-      <c r="S71" s="15"/>
-      <c r="T71" s="15"/>
-      <c r="U71" s="15"/>
-      <c r="V71" s="15"/>
-      <c r="W71" s="15"/>
+      <c r="Q71" s="18">
+        <f t="shared" ref="Q71:W71" si="1">Q70</f>
+        <v>8278.47</v>
+      </c>
+      <c r="R71" s="18">
+        <f t="shared" si="1"/>
+        <v>9372.02</v>
+      </c>
+      <c r="S71" s="18">
+        <f t="shared" si="1"/>
+        <v>17552.32</v>
+      </c>
+      <c r="T71" s="18">
+        <f t="shared" si="1"/>
+        <v>22358.82</v>
+      </c>
+      <c r="U71" s="18">
+        <f t="shared" si="1"/>
+        <v>25957.32</v>
+      </c>
+      <c r="V71" s="18">
+        <f t="shared" si="1"/>
+        <v>25374.26</v>
+      </c>
+      <c r="W71" s="18">
+        <f t="shared" si="1"/>
+        <v>26822.48</v>
+      </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
